--- a/data/nzd0568/nzd0568.xlsx
+++ b/data/nzd0568/nzd0568.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F968"/>
+  <dimension ref="A1:F970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23664,6 +23664,54 @@
         <v>220.37</v>
       </c>
       <c r="F968" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>214.72</v>
+      </c>
+      <c r="C969" t="n">
+        <v>220.65</v>
+      </c>
+      <c r="D969" t="n">
+        <v>224.82</v>
+      </c>
+      <c r="E969" t="n">
+        <v>220.84</v>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>215.63</v>
+      </c>
+      <c r="C970" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="D970" t="n">
+        <v>225.82</v>
+      </c>
+      <c r="E970" t="n">
+        <v>221.69</v>
+      </c>
+      <c r="F970" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23680,7 +23728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1096"/>
+  <dimension ref="A1:B1098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34643,6 +34691,26 @@
       </c>
       <c r="B1096" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1097" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1098" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -34805,28 +34873,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1574763747958309</v>
+        <v>0.1562249236946193</v>
       </c>
       <c r="J2" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="K2" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08309961132454224</v>
+        <v>0.08215570858770982</v>
       </c>
       <c r="M2" t="n">
-        <v>3.342666669998297</v>
+        <v>3.341737072510219</v>
       </c>
       <c r="N2" t="n">
-        <v>15.81028317154032</v>
+        <v>15.79717546621915</v>
       </c>
       <c r="O2" t="n">
-        <v>3.976214678754194</v>
+        <v>3.974566072695124</v>
       </c>
       <c r="P2" t="n">
-        <v>213.963909368328</v>
+        <v>213.9770534103234</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34877,28 +34945,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1066949010001283</v>
+        <v>0.1060956458311537</v>
       </c>
       <c r="J3" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="K3" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05662166037139316</v>
+        <v>0.05625185820004708</v>
       </c>
       <c r="M3" t="n">
-        <v>2.887499325248995</v>
+        <v>2.884325822228033</v>
       </c>
       <c r="N3" t="n">
-        <v>10.9591355013049</v>
+        <v>10.94112279077786</v>
       </c>
       <c r="O3" t="n">
-        <v>3.310458503184249</v>
+        <v>3.30773680796672</v>
       </c>
       <c r="P3" t="n">
-        <v>219.560537179766</v>
+        <v>219.5668307060354</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34949,28 +35017,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09522521390330842</v>
+        <v>0.09559786259241601</v>
       </c>
       <c r="J4" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="K4" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04337362855766824</v>
+        <v>0.04388948507937562</v>
       </c>
       <c r="M4" t="n">
-        <v>2.949020762759757</v>
+        <v>2.944893589661135</v>
       </c>
       <c r="N4" t="n">
-        <v>11.55596383199386</v>
+        <v>11.53430702925574</v>
       </c>
       <c r="O4" t="n">
-        <v>3.399406394062625</v>
+        <v>3.396219520180599</v>
       </c>
       <c r="P4" t="n">
-        <v>221.83495077551</v>
+        <v>221.8310342046714</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35021,28 +35089,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01232245105240014</v>
+        <v>0.01404790948731117</v>
       </c>
       <c r="J5" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="K5" t="n">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009260642880173364</v>
+        <v>0.001204292546892693</v>
       </c>
       <c r="M5" t="n">
-        <v>2.543538103733336</v>
+        <v>2.545919083899149</v>
       </c>
       <c r="N5" t="n">
-        <v>9.434285007987137</v>
+        <v>9.451276215775481</v>
       </c>
       <c r="O5" t="n">
-        <v>3.071528122610493</v>
+        <v>3.074292799291486</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7368493374707</v>
+        <v>216.7186783229054</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35080,7 +35148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F968"/>
+  <dimension ref="A1:F970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66055,6 +66123,70 @@
         </is>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>-41.026893994949226,173.01995277529994</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>-41.02623199132245,173.0195701727094</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>-41.02557761329514,173.01917705886834</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>-41.025005122070326,173.018908889426</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>-41.02689016174972,173.01996234360038</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>-41.0262291690998,173.01957721744793</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>-41.02557350762747,173.0191876465684</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>-41.02500512219356,173.0189190000792</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0568/nzd0568.xlsx
+++ b/data/nzd0568/nzd0568.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F970"/>
+  <dimension ref="A1:F974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23712,6 +23712,102 @@
         <v>221.69</v>
       </c>
       <c r="F970" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>216.37</v>
+      </c>
+      <c r="C971" t="n">
+        <v>221.89</v>
+      </c>
+      <c r="D971" t="n">
+        <v>226.48</v>
+      </c>
+      <c r="E971" t="n">
+        <v>221.98</v>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>216.49</v>
+      </c>
+      <c r="C972" t="n">
+        <v>221.88</v>
+      </c>
+      <c r="D972" t="n">
+        <v>226.56</v>
+      </c>
+      <c r="E972" t="n">
+        <v>221.69</v>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>217.42</v>
+      </c>
+      <c r="C973" t="n">
+        <v>222.46</v>
+      </c>
+      <c r="D973" t="n">
+        <v>226.72</v>
+      </c>
+      <c r="E973" t="n">
+        <v>221.57</v>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>217.72</v>
+      </c>
+      <c r="C974" t="n">
+        <v>222.54</v>
+      </c>
+      <c r="D974" t="n">
+        <v>226.79</v>
+      </c>
+      <c r="E974" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="F974" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23728,7 +23824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1098"/>
+  <dimension ref="A1:B1102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34711,6 +34807,46 @@
       </c>
       <c r="B1098" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1099" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1100" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1101" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1102" t="n">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>
@@ -34873,28 +35009,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1562249236946193</v>
+        <v>0.1552386326547342</v>
       </c>
       <c r="J2" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="K2" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08215570858770982</v>
+        <v>0.0818802520702937</v>
       </c>
       <c r="M2" t="n">
-        <v>3.341737072510219</v>
+        <v>3.332681042334635</v>
       </c>
       <c r="N2" t="n">
-        <v>15.79717546621915</v>
+        <v>15.73956114938185</v>
       </c>
       <c r="O2" t="n">
-        <v>3.974566072695124</v>
+        <v>3.967311577048348</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9770534103234</v>
+        <v>213.9874386187161</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34945,28 +35081,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1060956458311537</v>
+        <v>0.1058919306860061</v>
       </c>
       <c r="J3" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="K3" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05625185820004708</v>
+        <v>0.05654834464585623</v>
       </c>
       <c r="M3" t="n">
-        <v>2.884325822228033</v>
+        <v>2.873642751964133</v>
       </c>
       <c r="N3" t="n">
-        <v>10.94112279077786</v>
+        <v>10.89678373681535</v>
       </c>
       <c r="O3" t="n">
-        <v>3.30773680796672</v>
+        <v>3.301027678892642</v>
       </c>
       <c r="P3" t="n">
-        <v>219.5668307060354</v>
+        <v>219.5689738891246</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35017,28 +35153,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09559786259241601</v>
+        <v>0.0974018618560588</v>
       </c>
       <c r="J4" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="K4" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04388948507937562</v>
+        <v>0.04582259646853937</v>
       </c>
       <c r="M4" t="n">
-        <v>2.944893589661135</v>
+        <v>2.942185778816552</v>
       </c>
       <c r="N4" t="n">
-        <v>11.53430702925574</v>
+        <v>11.50685907469992</v>
       </c>
       <c r="O4" t="n">
-        <v>3.396219520180599</v>
+        <v>3.392176156201196</v>
       </c>
       <c r="P4" t="n">
-        <v>221.8310342046714</v>
+        <v>221.8120269901223</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35089,28 +35225,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01404790948731117</v>
+        <v>0.01781265559519666</v>
       </c>
       <c r="J5" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="K5" t="n">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001204292546892693</v>
+        <v>0.001935524547844292</v>
       </c>
       <c r="M5" t="n">
-        <v>2.545919083899149</v>
+        <v>2.552161549088414</v>
       </c>
       <c r="N5" t="n">
-        <v>9.451276215775481</v>
+        <v>9.498814418496448</v>
       </c>
       <c r="O5" t="n">
-        <v>3.074292799291486</v>
+        <v>3.082014668767241</v>
       </c>
       <c r="P5" t="n">
-        <v>216.7186783229054</v>
+        <v>216.6789200523563</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35148,7 +35284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F970"/>
+  <dimension ref="A1:F974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66187,6 +66323,134 @@
         </is>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>-41.02688704464183,173.01997012441532</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>-41.02622676810406,173.0195832107325</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>-41.025570797886274,173.01919463444975</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>-41.02500512223539,173.01892244959615</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>-41.026886539164835,173.01997138616903</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>-41.026226810226795,173.01958310558717</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>-41.02557046943276,173.01919548146563</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>-41.02500512219356,173.0189190000792</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>-41.02688262171758,173.01998116475957</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>-41.02622436710802,173.01958920401663</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>-41.025569812525724,173.01919717549737</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>-41.025005122176225,173.01891757269283</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>-41.02688135802474,173.01998431914336</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>-41.0262240301261,173.01959004517929</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>-41.02556952512888,173.01919791663624</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>-41.02500512218055,173.0189179295394</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0568/nzd0568.xlsx
+++ b/data/nzd0568/nzd0568.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F974"/>
+  <dimension ref="A1:F977"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23808,6 +23808,78 @@
         <v>221.6</v>
       </c>
       <c r="F974" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:16+00:00</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>218.6</v>
+      </c>
+      <c r="C975" t="n">
+        <v>222.75</v>
+      </c>
+      <c r="D975" t="n">
+        <v>226.87</v>
+      </c>
+      <c r="E975" t="n">
+        <v>221.3</v>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>218.73</v>
+      </c>
+      <c r="C976" t="n">
+        <v>222.98</v>
+      </c>
+      <c r="D976" t="n">
+        <v>226.85</v>
+      </c>
+      <c r="E976" t="n">
+        <v>221.48</v>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>218.86</v>
+      </c>
+      <c r="C977" t="n">
+        <v>222.97</v>
+      </c>
+      <c r="D977" t="n">
+        <v>226.47</v>
+      </c>
+      <c r="E977" t="n">
+        <v>221.14</v>
+      </c>
+      <c r="F977" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23824,7 +23896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1102"/>
+  <dimension ref="A1:B1105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34847,6 +34919,36 @@
       </c>
       <c r="B1102" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1103" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1104" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1105" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -35009,28 +35111,28 @@
         <v>0.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1552386326547342</v>
+        <v>0.1555553711679452</v>
       </c>
       <c r="J2" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="K2" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0818802520702937</v>
+        <v>0.08272059532481391</v>
       </c>
       <c r="M2" t="n">
-        <v>3.332681042334635</v>
+        <v>3.324112983674996</v>
       </c>
       <c r="N2" t="n">
-        <v>15.73956114938185</v>
+        <v>15.69203561044044</v>
       </c>
       <c r="O2" t="n">
-        <v>3.967311577048348</v>
+        <v>3.961317408443868</v>
       </c>
       <c r="P2" t="n">
-        <v>213.9874386187161</v>
+        <v>213.9840891444919</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35081,28 +35183,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1058919306860061</v>
+        <v>0.1061641488706232</v>
       </c>
       <c r="J3" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="K3" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05654834464585623</v>
+        <v>0.05720168342357546</v>
       </c>
       <c r="M3" t="n">
-        <v>2.873642751964133</v>
+        <v>2.866272722450452</v>
       </c>
       <c r="N3" t="n">
-        <v>10.89678373681535</v>
+        <v>10.86393162945611</v>
       </c>
       <c r="O3" t="n">
-        <v>3.301027678892642</v>
+        <v>3.296047880334281</v>
       </c>
       <c r="P3" t="n">
-        <v>219.5689738891246</v>
+        <v>219.566095261381</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35153,28 +35255,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0974018618560588</v>
+        <v>0.09878106470159873</v>
       </c>
       <c r="J4" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="K4" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04582259646853937</v>
+        <v>0.04732590720307761</v>
       </c>
       <c r="M4" t="n">
-        <v>2.942185778816552</v>
+        <v>2.940271695893687</v>
       </c>
       <c r="N4" t="n">
-        <v>11.50685907469992</v>
+        <v>11.48719738985915</v>
       </c>
       <c r="O4" t="n">
-        <v>3.392176156201196</v>
+        <v>3.389276824022958</v>
       </c>
       <c r="P4" t="n">
-        <v>221.8120269901223</v>
+        <v>221.797443579783</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35225,28 +35327,28 @@
         <v>0.1926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01781265559519666</v>
+        <v>0.02034427577032459</v>
       </c>
       <c r="J5" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="K5" t="n">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001935524547844292</v>
+        <v>0.002527334538579673</v>
       </c>
       <c r="M5" t="n">
-        <v>2.552161549088414</v>
+        <v>2.555596165658151</v>
       </c>
       <c r="N5" t="n">
-        <v>9.498814418496448</v>
+        <v>9.521966826580158</v>
       </c>
       <c r="O5" t="n">
-        <v>3.082014668767241</v>
+        <v>3.085768433726056</v>
       </c>
       <c r="P5" t="n">
-        <v>216.6789200523563</v>
+        <v>216.6520860731162</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35284,7 +35386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F974"/>
+  <dimension ref="A1:F977"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66451,6 +66553,102 @@
         </is>
       </c>
     </row>
+    <row r="975">
+      <c r="A975" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:16+00:00</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>-41.0268776511919,173.01999357200182</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>-41.026223145548514,173.01959225323117</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>-41.025569196675356,173.01919876365207</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>-41.02500512213714,173.0189143610736</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>-41.026877103591545,173.01999493890128</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>-41.0262221767254,173.01959467157369</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>-41.025569278788744,173.0191985518981</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>-41.02500512216319,173.01891650215308</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>-41.02687655599116,173.0199963058007</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>-41.02622221884814,173.01959456642837</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>-41.02557083894295,173.01919452857277</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>-41.02500512211394,173.01891245789182</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
